--- a/paper/submission/Supplementary-Table-4.xlsx
+++ b/paper/submission/Supplementary-Table-4.xlsx
@@ -4644,7 +4644,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Generated by src/nnrti/cli/build_supplementary_table_4.py from results/analysis/mechanisms/mechanism_coordinates.csv, results/analysis/mechanisms/dor_moiety_contacts_per_replicate.csv and results/analysis/modern_md_suite/tables/pocket_volume_per_rep.csv.</t>
+          <t>Generated by src/nnrti/cli/build_supplementary_table_4.py from results/analysis/mechanisms/mechanism_coordinates.csv, results/analysis/mechanisms/dor_moiety_contacts_per_replicate.csv and results/analysis/pocket_volume/tables/pocket_volume_per_rep.csv.</t>
         </is>
       </c>
     </row>
